--- a/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 3.xlsx
+++ b/exercise/Admin/Admin Hotel/Tes Excel Admin Hotel 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Hotel 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Hotel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE8EC91-D0F9-46B7-99A8-5107BD26228B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0FE4B2-1793-4818-A758-709D2C2B2286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -340,10 +349,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -666,12 +675,12 @@
       <c r="C1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
@@ -724,10 +733,22 @@
       <c r="G3" s="6">
         <v>5</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="14"/>
+      <c r="H3" s="14" t="str">
+        <f>VLOOKUP(E3,$B$15:$C$20,2,FALSE)</f>
+        <v>III</v>
+      </c>
+      <c r="I3" s="14">
+        <f>VLOOKUP(H3,$E$15:$F$20,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="J3" s="12">
+        <f>IF(D3&lt;DATE(2017,12,10),10%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="14">
+        <f>(G3*I3)-(G3*I3*J3)</f>
+        <v>70</v>
+      </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -748,10 +769,22 @@
       <c r="G4" s="6">
         <v>3</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="14"/>
+      <c r="H4" s="14" t="str">
+        <f t="shared" ref="H4:H12" si="0">VLOOKUP(E4,$B$15:$C$20,2,FALSE)</f>
+        <v>IV</v>
+      </c>
+      <c r="I4" s="14">
+        <f t="shared" ref="I4:I12" si="1">VLOOKUP(H4,$E$15:$F$20,2,FALSE)</f>
+        <v>12</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" ref="J4:J12" si="2">IF(D4&lt;DATE(2017,12,10),10%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K12" si="3">(G4*I4)-(G4*I4*J4)</f>
+        <v>36</v>
+      </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
@@ -772,10 +805,22 @@
       <c r="G5" s="6">
         <v>6</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="14"/>
+      <c r="H5" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>V</v>
+      </c>
+      <c r="I5" s="14">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
@@ -796,10 +841,22 @@
       <c r="G6" s="6">
         <v>5</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="14"/>
+      <c r="H6" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>IV</v>
+      </c>
+      <c r="I6" s="14">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="14">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
@@ -820,10 +877,22 @@
       <c r="G7" s="6">
         <v>3</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="14"/>
+      <c r="H7" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>I</v>
+      </c>
+      <c r="I7" s="14">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="14">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
@@ -844,10 +913,22 @@
       <c r="G8" s="6">
         <v>5</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="14"/>
+      <c r="H8" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>I</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
@@ -868,10 +949,22 @@
       <c r="G9" s="6">
         <v>3</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="14"/>
+      <c r="H9" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>II</v>
+      </c>
+      <c r="I9" s="14">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
@@ -892,10 +985,22 @@
       <c r="G10" s="6">
         <v>5</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="14"/>
+      <c r="H10" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>III</v>
+      </c>
+      <c r="I10" s="14">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="14">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
@@ -916,10 +1021,22 @@
       <c r="G11" s="6">
         <v>6</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="14"/>
+      <c r="H11" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>II</v>
+      </c>
+      <c r="I11" s="14">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="K11" s="14">
+        <f t="shared" si="3"/>
+        <v>86.4</v>
+      </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
@@ -940,10 +1057,22 @@
       <c r="G12" s="6">
         <v>6</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="14"/>
+      <c r="H12" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>V</v>
+      </c>
+      <c r="I12" s="14">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="14">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="13" spans="2:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:13" x14ac:dyDescent="0.3">
@@ -1005,8 +1134,14 @@
       <c r="H16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="14">
+        <f>COUNTIF($H$3:$H$12,H16)</f>
+        <v>2</v>
+      </c>
+      <c r="J16" s="14">
+        <f>SUMIF($H$3:$H$12,H16,$K$3:$K$12)</f>
+        <v>154</v>
+      </c>
       <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="13"/>
@@ -1027,8 +1162,14 @@
       <c r="H17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+      <c r="I17" s="14">
+        <f t="shared" ref="I17:I20" si="4">COUNTIF($H$3:$H$12,H17)</f>
+        <v>2</v>
+      </c>
+      <c r="J17" s="14">
+        <f t="shared" ref="J17:J20" si="5">SUMIF($H$3:$H$12,H17,$K$3:$K$12)</f>
+        <v>134.4</v>
+      </c>
       <c r="K17" s="17"/>
       <c r="L17" s="17"/>
     </row>
@@ -1048,8 +1189,14 @@
       <c r="H18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="I18" s="14">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J18" s="14">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
       <c r="K18" s="17"/>
       <c r="L18" s="17"/>
     </row>
@@ -1069,8 +1216,14 @@
       <c r="H19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+      <c r="I19" s="14">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J19" s="14">
+        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
     </row>
@@ -1090,8 +1243,14 @@
       <c r="H20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
+      <c r="I20" s="14">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J20" s="14">
+        <f t="shared" si="5"/>
+        <v>114</v>
+      </c>
       <c r="K20" s="17"/>
       <c r="L20" s="17"/>
     </row>
